--- a/public/sap-reporting/expansion-150-downloads/EXT-SD14-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-SD14-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R9d7e0aa6dd1c41aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rf303d3c7427b4d16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R74ac723269374da8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R186f3cb398194a36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rec4db737eeee4a1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R88493d685b1b4feb"/>
   </x:sheets>
 </x:workbook>
 </file>
